--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Levels.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Levels.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CCA\Src\Assets\Common\Tables\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CCA\Src\Assets\StreamingAssets\Common\Tables\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D844D4-FB68-49A2-A173-DEFD26354D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6247C4EC-EC8E-4121-BA6E-53C15E5AA14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="491">
   <si>
     <t>Key</t>
   </si>
@@ -102,9 +102,6 @@
     <t>Skunk Chieftain</t>
   </si>
   <si>
-    <t>臭鼬头领</t>
-  </si>
-  <si>
     <t>Dagger of Void</t>
   </si>
   <si>
@@ -1162,10 +1159,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>[["Toy Warrior","Toy Warrior","Toy Warrior"]]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>[["Toy Factory"]]</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1178,10 +1171,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>[["Furious Skunk","Skunk Slave"],["Skunk Chieftain"]]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>[["Shadow of Void","Chronos Hand","Mnemosyne Hand"]]</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1686,10 +1675,6 @@
   </si>
   <si>
     <t>["rebounce"]</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>["bullet","shoot","double_shoot","double_block","rebounce"]</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -1914,39 +1899,6 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>["Entity of Will"]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>]</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
       <t>["Counter-Blade"]</t>
     </r>
     <r>
@@ -2006,6 +1958,50 @@
   <si>
     <t>[4,0,0]</t>
     <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>臭鼬头领</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[["Toy Warrior","Toy Warrior","Toy Warrior"]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["stab"]</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>[["Furious Skunk","Skunk Slave"],["Skunk Chieftain","Black Coat","Black Coat"]]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2834,22 +2830,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -2864,7 +2860,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" s="7">
         <v>4</v>
@@ -2897,7 +2893,7 @@
         <v>21</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D3" s="10">
         <v>2</v>
@@ -2924,13 +2920,13 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D4" s="7">
         <v>2</v>
@@ -2963,7 +2959,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" s="11">
         <v>2</v>
@@ -2992,7 +2988,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D6" s="7">
         <v>7</v>
@@ -3025,7 +3021,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7" s="11">
         <v>5</v>
@@ -3093,31 +3089,31 @@
         <v>3</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="I1" s="3"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="D2" s="6">
         <v>7</v>
@@ -3126,7 +3122,7 @@
         <v>100</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2" s="7">
         <v>0.7</v>
@@ -3138,13 +3134,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>65</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>66</v>
       </c>
       <c r="D3" s="9">
         <v>3</v>
@@ -3153,7 +3149,7 @@
         <v>7</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3" s="10">
         <v>0.4</v>
@@ -3165,13 +3161,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="D4" s="6">
         <v>0</v>
@@ -3180,7 +3176,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G4" s="7">
         <v>0.3</v>
@@ -3230,13 +3226,13 @@
         <v>2</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="F1" s="22" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="H1" s="22" t="s">
         <v>8</v>
@@ -3254,10 +3250,10 @@
         <v>7</v>
       </c>
       <c r="M1" s="36" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N1" s="36" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O1" s="22"/>
       <c r="P1" s="22"/>
@@ -3265,27 +3261,27 @@
     </row>
     <row r="2" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B2" s="4" t="str">
         <f>A2</f>
         <v>Toy Grunt</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F2" s="26" t="b">
         <v>0</v>
       </c>
       <c r="G2" s="26"/>
       <c r="H2" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I2" s="26" t="s">
         <v>11</v>
@@ -3298,13 +3294,13 @@
         <v>2</v>
       </c>
       <c r="L2" s="26" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N2" s="26" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -3312,26 +3308,26 @@
     </row>
     <row r="3" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B3" s="27" t="str">
         <f t="shared" ref="B3:B21" si="0">A3</f>
         <v>Toy Warrior</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F3" s="16" t="b">
         <v>0</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>11</v>
@@ -3347,28 +3343,28 @@
         <v>12</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" s="28" t="str">
         <f t="shared" si="0"/>
         <v>Toy Guardian</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F4" s="6" t="b">
         <v>0</v>
@@ -3391,10 +3387,10 @@
         <v>12</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
@@ -3402,20 +3398,20 @@
     </row>
     <row r="5" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" s="29" t="str">
         <f t="shared" si="0"/>
         <v>Toy Minion</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F5" s="16" t="b">
         <v>0</v>
@@ -3437,28 +3433,28 @@
         <v>12</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B6" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Toy Gentleman</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F6" s="60" t="b">
         <v>1</v>
@@ -3478,13 +3474,13 @@
         <v>4</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
@@ -3492,26 +3488,26 @@
     </row>
     <row r="7" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B7" s="29" t="str">
         <f t="shared" si="0"/>
         <v>Toy Factory</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F7" s="16" t="b">
         <v>0</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>11</v>
@@ -3524,38 +3520,38 @@
         <v>7</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N7" s="29" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B8" s="33" t="str">
         <f t="shared" si="0"/>
         <v>Swordsman of Faith</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F8" s="33" t="b">
         <v>0</v>
       </c>
       <c r="G8" s="33"/>
       <c r="H8" s="33" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I8" s="33" t="s">
         <v>11</v>
@@ -3568,13 +3564,13 @@
         <v>4</v>
       </c>
       <c r="L8" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M8" s="33" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N8" s="33" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O8" s="33"/>
       <c r="P8" s="33"/>
@@ -3595,12 +3591,14 @@
         <v>13</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F9" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="G9" s="11"/>
+      <c r="G9" s="11" t="s">
+        <v>488</v>
+      </c>
       <c r="H9" s="11" t="s">
         <v>16</v>
       </c>
@@ -3618,10 +3616,10 @@
         <v>12</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3636,15 +3634,17 @@
         <v>20</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F10" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="G10" s="32"/>
+      <c r="G10" s="32" t="s">
+        <v>488</v>
+      </c>
       <c r="H10" s="32" t="s">
         <v>16</v>
       </c>
@@ -3662,10 +3662,10 @@
         <v>12</v>
       </c>
       <c r="M10" s="32" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N10" s="32" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O10" s="32"/>
       <c r="P10" s="32"/>
@@ -3673,20 +3673,20 @@
     </row>
     <row r="11" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B11" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Furious Skunk</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F11" s="11" t="b">
         <v>0</v>
@@ -3709,15 +3709,15 @@
         <v>12</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B12" s="32" t="str">
         <f t="shared" si="0"/>
@@ -3727,10 +3727,10 @@
         <v>22</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F12" s="32" t="b">
         <v>0</v>
@@ -3753,10 +3753,10 @@
         <v>12</v>
       </c>
       <c r="M12" s="32" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N12" s="32" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O12" s="32"/>
       <c r="P12" s="32"/>
@@ -3771,19 +3771,19 @@
         <v>Skunk Chieftain</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>24</v>
+        <v>486</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F13" s="11" t="b">
         <v>0</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>11</v>
@@ -3799,31 +3799,31 @@
         <v>7</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>12</v>
+        <v>354</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>420</v>
-      </c>
-      <c r="N13" s="29" t="s">
-        <v>362</v>
+        <v>417</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B14" s="33" t="str">
         <f t="shared" si="0"/>
         <v>Shadow of Void</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F14" s="33" t="b">
         <v>0</v>
@@ -3843,13 +3843,13 @@
         <v>6</v>
       </c>
       <c r="L14" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M14" s="33" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N14" s="33" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="O14" s="33"/>
       <c r="P14" s="33"/>
@@ -3857,20 +3857,20 @@
     </row>
     <row r="15" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B15" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Void Beast</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F15" s="11" t="b">
         <v>0</v>
@@ -3892,37 +3892,37 @@
         <v>1</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N15" s="29" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B16" s="32" t="str">
         <f t="shared" si="0"/>
         <v>Chronos Hand</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F16" s="32" t="b">
         <v>0</v>
       </c>
       <c r="G16" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H16" s="32" t="s">
         <v>11</v>
@@ -3941,10 +3941,10 @@
         <v>12</v>
       </c>
       <c r="M16" s="32" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N16" s="33" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="O16" s="32"/>
       <c r="P16" s="32"/>
@@ -3952,26 +3952,26 @@
     </row>
     <row r="17" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B17" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Mnemosyne Hand</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F17" s="11" t="b">
         <v>0</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H17" s="11" t="s">
         <v>11</v>
@@ -3990,28 +3990,28 @@
         <v>12</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N17" s="29" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B18" s="32" t="str">
         <f t="shared" si="0"/>
         <v>Entity of Will</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F18" s="54" t="b">
         <v>1</v>
@@ -4029,10 +4029,10 @@
         <v>12</v>
       </c>
       <c r="M18" s="32" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N18" s="33" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="O18" s="32"/>
       <c r="P18" s="32"/>
@@ -4040,27 +4040,27 @@
     </row>
     <row r="19" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Dagger of Void</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F19" s="11" t="b">
         <v>0</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I19" s="11" t="s">
         <v>11</v>
@@ -4076,28 +4076,28 @@
         <v>12</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B20" s="32" t="str">
         <f t="shared" si="0"/>
         <v>Sword of Shadow</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F20" s="32" t="b">
         <v>0</v>
@@ -4107,7 +4107,7 @@
         <v>16</v>
       </c>
       <c r="I20" s="33" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="J20" s="32">
         <v>2</v>
@@ -4117,13 +4117,13 @@
         <v>2</v>
       </c>
       <c r="L20" s="33" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="M20" s="32" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N20" s="33" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="O20" s="32"/>
       <c r="P20" s="32"/>
@@ -4131,26 +4131,26 @@
     </row>
     <row r="21" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B21" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Stronghold Chieftain</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F21" s="29" t="b">
         <v>0</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="H21" s="11" t="s">
         <v>11</v>
@@ -4166,37 +4166,37 @@
         <v>16</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N21" s="29" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B22" s="34" t="str">
         <f>A22</f>
         <v>Arbiter of Divine</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F22" s="34" t="b">
         <v>0</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H22" s="34" t="s">
         <v>11</v>
@@ -4215,10 +4215,10 @@
         <v>12</v>
       </c>
       <c r="M22" s="34" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N22" s="53" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="O22" s="34"/>
       <c r="P22" s="34"/>
@@ -4226,26 +4226,26 @@
     </row>
     <row r="23" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B23" s="29" t="str">
         <f t="shared" ref="B23:B81" si="2">A23</f>
         <v>Judge of Divine</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E23" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F23" s="29" t="b">
         <v>0</v>
       </c>
       <c r="G23" s="29" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H23" s="29" t="s">
         <v>11</v>
@@ -4261,13 +4261,13 @@
         <v>6</v>
       </c>
       <c r="L23" s="29" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M23" s="29" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N23" s="29" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="O23" s="29"/>
       <c r="P23" s="29"/>
@@ -4275,26 +4275,26 @@
     </row>
     <row r="24" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="34" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B24" s="34" t="str">
         <f t="shared" si="2"/>
         <v>Butaro</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E24" s="34" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F24" s="34" t="b">
         <v>0</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H24" s="34" t="s">
         <v>11</v>
@@ -4310,13 +4310,13 @@
         <v>6</v>
       </c>
       <c r="L24" s="34" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M24" s="34" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N24" s="34" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O24" s="34"/>
       <c r="P24" s="34"/>
@@ -4324,20 +4324,20 @@
     </row>
     <row r="25" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B25" s="29" t="str">
         <f t="shared" si="2"/>
         <v>Huntaro</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F25" s="29" t="b">
         <v>0</v>
@@ -4357,13 +4357,13 @@
         <v>3</v>
       </c>
       <c r="L25" s="29" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M25" s="29" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N25" s="29" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="O25" s="29"/>
       <c r="P25" s="29"/>
@@ -4371,27 +4371,27 @@
     </row>
     <row r="26" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B26" s="34" t="str">
         <f t="shared" si="2"/>
         <v>Weasel Bandit</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D26" s="34" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E26" s="34" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F26" s="34" t="b">
         <v>0</v>
       </c>
       <c r="G26" s="34"/>
       <c r="H26" s="34" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I26" s="34" t="s">
         <v>11</v>
@@ -4407,10 +4407,10 @@
         <v>12</v>
       </c>
       <c r="M26" s="34" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N26" s="34" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O26" s="34"/>
       <c r="P26" s="34"/>
@@ -4418,20 +4418,20 @@
     </row>
     <row r="27" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B27" s="29" t="str">
         <f t="shared" si="2"/>
         <v>One-Eye</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E27" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F27" s="29" t="b">
         <v>0</v>
@@ -4451,13 +4451,13 @@
         <v>9</v>
       </c>
       <c r="L27" s="29" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M27" s="29" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N27" s="29" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="O27" s="29"/>
       <c r="P27" s="29"/>
@@ -4465,26 +4465,26 @@
     </row>
     <row r="28" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="34" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B28" s="34" t="str">
         <f t="shared" si="2"/>
         <v>Weasel Lackey</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D28" s="34" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E28" s="34" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F28" s="34" t="b">
         <v>0</v>
       </c>
       <c r="G28" s="34" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H28" s="34" t="s">
         <v>11</v>
@@ -4503,10 +4503,10 @@
         <v>12</v>
       </c>
       <c r="M28" s="34" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N28" s="34" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O28" s="34"/>
       <c r="P28" s="34"/>
@@ -4514,26 +4514,26 @@
     </row>
     <row r="29" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B29" s="29" t="str">
         <f t="shared" si="2"/>
         <v>Left Guard</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F29" s="29" t="b">
         <v>0</v>
       </c>
       <c r="G29" s="29" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H29" s="29" t="s">
         <v>11</v>
@@ -4549,13 +4549,13 @@
         <v>5</v>
       </c>
       <c r="L29" s="29" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M29" s="29" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N29" s="29" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O29" s="29"/>
       <c r="P29" s="29"/>
@@ -4563,26 +4563,26 @@
     </row>
     <row r="30" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="34" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B30" s="34" t="str">
         <f t="shared" si="2"/>
         <v>Right Guard</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D30" s="34" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E30" s="34" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F30" s="34" t="b">
         <v>0</v>
       </c>
       <c r="G30" s="34" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H30" s="34" t="s">
         <v>11</v>
@@ -4598,13 +4598,13 @@
         <v>4</v>
       </c>
       <c r="L30" s="34" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M30" s="34" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N30" s="34" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O30" s="34"/>
       <c r="P30" s="34"/>
@@ -4612,20 +4612,20 @@
     </row>
     <row r="31" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B31" s="29" t="str">
         <f t="shared" si="2"/>
         <v>Guard Captain</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F31" s="29" t="b">
         <v>0</v>
@@ -4645,13 +4645,13 @@
         <v>6</v>
       </c>
       <c r="L31" s="29" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M31" s="29" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N31" s="29" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="O31" s="29"/>
       <c r="P31" s="29"/>
@@ -4659,26 +4659,26 @@
     </row>
     <row r="32" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="53" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B32" s="34" t="str">
         <f>A32</f>
         <v>Shadow_1</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D32" s="34" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E32" s="34" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F32" s="34" t="b">
         <v>0</v>
       </c>
       <c r="G32" s="53" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>11</v>
@@ -4694,13 +4694,13 @@
         <v>6</v>
       </c>
       <c r="L32" s="34" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M32" s="34" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N32" s="53" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="O32" s="34"/>
       <c r="P32" s="34"/>
@@ -4708,26 +4708,26 @@
     </row>
     <row r="33" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B33" s="29" t="str">
         <f>A33</f>
         <v>Shadow_2</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E33" s="29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F33" s="29" t="b">
         <v>0</v>
       </c>
       <c r="G33" s="29" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="H33" s="29" t="s">
         <v>11</v>
@@ -4743,13 +4743,13 @@
         <v>8</v>
       </c>
       <c r="L33" s="29" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M33" s="29" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N33" s="29" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="O33" s="29"/>
       <c r="P33" s="29"/>
@@ -4757,26 +4757,26 @@
     </row>
     <row r="34" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="34" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B34" s="34" t="str">
         <f t="shared" si="2"/>
         <v>Shadow_3</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D34" s="34" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E34" s="34" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F34" s="34" t="b">
         <v>0</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="H34" s="34" t="s">
         <v>11</v>
@@ -4795,10 +4795,10 @@
         <v>12</v>
       </c>
       <c r="M34" s="34" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N34" s="53" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="O34" s="34"/>
       <c r="P34" s="34"/>
@@ -4806,26 +4806,26 @@
     </row>
     <row r="35" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B35" s="29" t="str">
         <f t="shared" si="2"/>
         <v>Hand-Mirage</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F35" s="29" t="b">
         <v>0</v>
       </c>
       <c r="G35" s="29" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H35" s="29" t="s">
         <v>11</v>
@@ -4841,13 +4841,13 @@
         <v>9</v>
       </c>
       <c r="L35" s="29" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M35" s="29" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N35" s="29" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="O35" s="29"/>
       <c r="P35" s="29"/>
@@ -4855,20 +4855,20 @@
     </row>
     <row r="36" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B36" s="34" t="str">
         <f t="shared" si="2"/>
         <v>Cleric</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D36" s="34" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E36" s="34" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F36" s="34" t="b">
         <v>0</v>
@@ -4888,13 +4888,13 @@
         <v>5</v>
       </c>
       <c r="L36" s="34" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M36" s="34" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N36" s="53" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="O36" s="34"/>
       <c r="P36" s="34"/>
@@ -4902,20 +4902,20 @@
     </row>
     <row r="37" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B37" s="29" t="str">
         <f>A37</f>
         <v>Prism Dancer_1</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F37" s="29" t="b">
         <v>0</v>
@@ -4935,13 +4935,13 @@
         <v>4</v>
       </c>
       <c r="L37" s="29" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M37" s="29" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N37" s="29" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="O37" s="29"/>
       <c r="P37" s="29"/>
@@ -4949,20 +4949,20 @@
     </row>
     <row r="38" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="37" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B38" s="37" t="str">
         <f t="shared" ref="B38" si="3">A38</f>
         <v>Prism Dancer_2</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F38" s="37" t="b">
         <v>0</v>
@@ -4982,13 +4982,13 @@
         <v>4</v>
       </c>
       <c r="L38" s="37" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M38" s="37" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N38" s="37" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="O38" s="37"/>
       <c r="P38" s="37"/>
@@ -4996,26 +4996,26 @@
     </row>
     <row r="39" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="38" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B39" s="11" t="str">
         <f t="shared" si="2"/>
         <v>Bog Monkey</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F39" s="11" t="b">
         <v>0</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H39" s="11" t="s">
         <v>11</v>
@@ -5034,28 +5034,28 @@
         <v>12</v>
       </c>
       <c r="M39" s="11" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N39" s="29" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="39" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B40" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Bog Sage</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D40" s="39" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E40" s="39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F40" s="39" t="b">
         <v>0</v>
@@ -5075,13 +5075,13 @@
         <v>8</v>
       </c>
       <c r="L40" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M40" s="39" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N40" s="39" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="O40" s="39"/>
       <c r="P40" s="39"/>
@@ -5089,26 +5089,26 @@
     </row>
     <row r="41" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="38" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B41" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Rubber Logistics Soldier</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F41" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G41" s="38" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H41" s="38" t="s">
         <v>11</v>
@@ -5124,13 +5124,13 @@
         <v>2</v>
       </c>
       <c r="L41" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M41" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N41" s="38" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="O41" s="38"/>
       <c r="P41" s="38"/>
@@ -5138,26 +5138,26 @@
     </row>
     <row r="42" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="39" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B42" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Tiger</v>
       </c>
       <c r="C42" s="39" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D42" s="39" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E42" s="39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F42" s="39" t="b">
         <v>0</v>
       </c>
       <c r="G42" s="39" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H42" s="39" t="s">
         <v>11</v>
@@ -5173,13 +5173,13 @@
         <v>8</v>
       </c>
       <c r="L42" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M42" s="39" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N42" s="39" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="O42" s="39"/>
       <c r="P42" s="39"/>
@@ -5187,26 +5187,26 @@
     </row>
     <row r="43" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="38" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B43" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Ghost Warrior</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E43" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F43" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G43" s="38" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H43" s="38" t="s">
         <v>11</v>
@@ -5222,13 +5222,13 @@
         <v>2</v>
       </c>
       <c r="L43" s="38" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="M43" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N43" s="38" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="O43" s="38"/>
       <c r="P43" s="38"/>
@@ -5236,29 +5236,29 @@
     </row>
     <row r="44" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B44" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Gustav Railway Cannon</v>
       </c>
       <c r="C44" s="39" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D44" s="39" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E44" s="39" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F44" s="39" t="b">
         <v>0</v>
       </c>
       <c r="G44" s="39" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H44" s="39" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="I44" s="39" t="s">
         <v>11</v>
@@ -5271,13 +5271,13 @@
         <v>12</v>
       </c>
       <c r="L44" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M44" s="39" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N44" s="39" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="O44" s="39"/>
       <c r="P44" s="39"/>
@@ -5285,29 +5285,29 @@
     </row>
     <row r="45" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="38" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B45" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Rubber Artillery</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F45" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G45" s="38" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I45" s="38" t="s">
         <v>11</v>
@@ -5320,13 +5320,13 @@
         <v>3</v>
       </c>
       <c r="L45" s="38" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="M45" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N45" s="38" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="O45" s="38"/>
       <c r="P45" s="38"/>
@@ -5334,26 +5334,26 @@
     </row>
     <row r="46" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="39" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B46" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Voidwarden of Pale</v>
       </c>
       <c r="C46" s="39" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D46" s="39" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E46" s="39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F46" s="39" t="b">
         <v>0</v>
       </c>
       <c r="G46" s="39" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H46" s="39" t="s">
         <v>11</v>
@@ -5369,13 +5369,13 @@
         <v>8</v>
       </c>
       <c r="L46" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M46" s="39" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N46" s="39" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="O46" s="39"/>
       <c r="P46" s="39"/>
@@ -5383,26 +5383,26 @@
     </row>
     <row r="47" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="38" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B47" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Voidwarden of Abyss</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E47" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F47" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G47" s="38" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H47" s="38" t="s">
         <v>11</v>
@@ -5418,13 +5418,13 @@
         <v>8</v>
       </c>
       <c r="L47" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M47" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N47" s="38" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="O47" s="38"/>
       <c r="P47" s="38"/>
@@ -5432,26 +5432,26 @@
     </row>
     <row r="48" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="39" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B48" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Cursed Tree</v>
       </c>
       <c r="C48" s="39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D48" s="39" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E48" s="39" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F48" s="39" t="b">
         <v>0</v>
       </c>
       <c r="G48" s="39" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H48" s="39" t="s">
         <v>11</v>
@@ -5467,13 +5467,13 @@
         <v>14</v>
       </c>
       <c r="L48" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M48" s="39" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N48" s="39" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="O48" s="39"/>
       <c r="P48" s="39"/>
@@ -5481,26 +5481,26 @@
     </row>
     <row r="49" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B49" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Porcupine</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E49" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F49" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G49" s="38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H49" s="38" t="s">
         <v>11</v>
@@ -5516,13 +5516,13 @@
         <v>5</v>
       </c>
       <c r="L49" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M49" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N49" s="38" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="O49" s="38"/>
       <c r="P49" s="38"/>
@@ -5530,26 +5530,26 @@
     </row>
     <row r="50" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="39" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B50" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Tree Spirit</v>
       </c>
       <c r="C50" s="39" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D50" s="39" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E50" s="39" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F50" s="39" t="b">
         <v>0</v>
       </c>
       <c r="G50" s="39" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H50" s="39" t="s">
         <v>11</v>
@@ -5565,13 +5565,13 @@
         <v>3</v>
       </c>
       <c r="L50" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M50" s="39" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N50" s="39" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="O50" s="39"/>
       <c r="P50" s="39"/>
@@ -5579,27 +5579,27 @@
     </row>
     <row r="51" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B51" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Coyote</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D51" s="43" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E51" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F51" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" s="38" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I51" s="38" t="s">
         <v>11</v>
@@ -5612,13 +5612,13 @@
         <v>2</v>
       </c>
       <c r="L51" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M51" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N51" s="38" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="O51" s="38"/>
       <c r="P51" s="38"/>
@@ -5626,18 +5626,18 @@
     </row>
     <row r="52" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="39" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B52" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Brave·Left Hand</v>
       </c>
       <c r="C52" s="39" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D52" s="45"/>
       <c r="E52" s="39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F52" s="39" t="b">
         <v>0</v>
@@ -5657,13 +5657,13 @@
         <v>9</v>
       </c>
       <c r="L52" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M52" s="39" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N52" s="39" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O52" s="39"/>
       <c r="P52" s="39"/>
@@ -5671,18 +5671,18 @@
     </row>
     <row r="53" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="38" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B53" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Brave·Right Hand</v>
       </c>
       <c r="C53" s="42" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D53" s="46"/>
       <c r="E53" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F53" s="38" t="b">
         <v>0</v>
@@ -5702,13 +5702,13 @@
         <v>9</v>
       </c>
       <c r="L53" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M53" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N53" s="38" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O53" s="38"/>
       <c r="P53" s="38"/>
@@ -5716,27 +5716,27 @@
     </row>
     <row r="54" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B54" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Fear</v>
       </c>
       <c r="C54" s="39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D54" s="39" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E54" s="39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F54" s="39" t="b">
         <v>0</v>
       </c>
       <c r="G54" s="39"/>
       <c r="H54" s="39" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I54" s="39" t="s">
         <v>11</v>
@@ -5749,13 +5749,13 @@
         <v>6</v>
       </c>
       <c r="L54" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M54" s="39" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N54" s="39" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="O54" s="39"/>
       <c r="P54" s="39"/>
@@ -5763,20 +5763,20 @@
     </row>
     <row r="55" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="38" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B55" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Unbroken Will</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E55" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F55" s="38" t="b">
         <v>0</v>
@@ -5796,13 +5796,13 @@
         <v>4</v>
       </c>
       <c r="L55" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M55" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N55" s="38" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="O55" s="38"/>
       <c r="P55" s="38"/>
@@ -5810,26 +5810,26 @@
     </row>
     <row r="56" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B56" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Brave of Old</v>
       </c>
       <c r="C56" s="39" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D56" s="39" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E56" s="39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F56" s="39" t="b">
         <v>0</v>
       </c>
       <c r="G56" s="39" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H56" s="39" t="s">
         <v>11</v>
@@ -5845,13 +5845,13 @@
         <v>8</v>
       </c>
       <c r="L56" s="39" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="M56" s="39" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N56" s="39" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="O56" s="39"/>
       <c r="P56" s="39"/>
@@ -5859,26 +5859,26 @@
     </row>
     <row r="57" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="38" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B57" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Ancestral Brave</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E57" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F57" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G57" s="38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H57" s="38" t="s">
         <v>11</v>
@@ -5894,13 +5894,13 @@
         <v>15</v>
       </c>
       <c r="L57" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M57" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N57" s="38" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="O57" s="38"/>
       <c r="P57" s="38"/>
@@ -5908,26 +5908,26 @@
     </row>
     <row r="58" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="39" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B58" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Oathblade</v>
       </c>
       <c r="C58" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D58" s="39" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E58" s="39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F58" s="39" t="b">
         <v>0</v>
       </c>
       <c r="G58" s="39" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H58" s="39" t="s">
         <v>11</v>
@@ -5943,13 +5943,13 @@
         <v>8</v>
       </c>
       <c r="L58" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M58" s="39" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N58" s="39" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="O58" s="39"/>
       <c r="P58" s="39"/>
@@ -5957,20 +5957,20 @@
     </row>
     <row r="59" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B59" s="11" t="str">
         <f t="shared" si="2"/>
         <v>Void Lock</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F59" s="11" t="b">
         <v>0</v>
@@ -5987,28 +5987,28 @@
         <v>12</v>
       </c>
       <c r="M59" s="11" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N59" s="29" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="41" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B60" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Void Cage</v>
       </c>
       <c r="C60" s="41" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D60" s="41" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E60" s="41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F60" s="41" t="b">
         <v>0</v>
@@ -6024,13 +6024,13 @@
         <v>8</v>
       </c>
       <c r="L60" s="41" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M60" s="41" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N60" s="41" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="O60" s="41"/>
       <c r="P60" s="41"/>
@@ -6038,26 +6038,26 @@
     </row>
     <row r="61" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B61" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Rat</v>
       </c>
       <c r="C61" s="38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D61" s="38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E61" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F61" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G61" s="38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H61" s="38"/>
       <c r="I61" s="38"/>
@@ -6069,13 +6069,13 @@
         <v>3</v>
       </c>
       <c r="L61" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M61" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N61" s="38" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O61" s="38"/>
       <c r="P61" s="38"/>
@@ -6083,26 +6083,26 @@
     </row>
     <row r="62" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="41" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B62" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Rat King</v>
       </c>
       <c r="C62" s="41" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D62" s="41" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E62" s="41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F62" s="41" t="b">
         <v>0</v>
       </c>
       <c r="G62" s="41" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H62" s="41"/>
       <c r="I62" s="41"/>
@@ -6114,13 +6114,13 @@
         <v>10</v>
       </c>
       <c r="L62" s="41" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M62" s="41" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N62" s="41" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="O62" s="41"/>
       <c r="P62" s="41"/>
@@ -6128,20 +6128,20 @@
     </row>
     <row r="63" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B63" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Frog</v>
       </c>
       <c r="C63" s="38" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D63" s="38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E63" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F63" s="38" t="b">
         <v>0</v>
@@ -6157,13 +6157,13 @@
         <v>7</v>
       </c>
       <c r="L63" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M63" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N63" s="38" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="O63" s="38"/>
       <c r="P63" s="38"/>
@@ -6171,20 +6171,20 @@
     </row>
     <row r="64" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="41" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B64" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Horse</v>
       </c>
       <c r="C64" s="41" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D64" s="41" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E64" s="41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F64" s="41" t="b">
         <v>0</v>
@@ -6200,13 +6200,13 @@
         <v>9</v>
       </c>
       <c r="L64" s="41" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M64" s="41" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N64" s="41" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O64" s="41"/>
       <c r="P64" s="41"/>
@@ -6214,20 +6214,20 @@
     </row>
     <row r="65" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="38" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B65" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Fruit Fly</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D65" s="38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E65" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F65" s="38" t="b">
         <v>0</v>
@@ -6243,13 +6243,13 @@
         <v>2</v>
       </c>
       <c r="L65" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M65" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N65" s="38" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="O65" s="38"/>
       <c r="P65" s="38"/>
@@ -6257,20 +6257,20 @@
     </row>
     <row r="66" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="41" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B66" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Unsoiled Seed</v>
       </c>
       <c r="C66" s="41" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D66" s="41" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E66" s="41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F66" s="41" t="b">
         <v>0</v>
@@ -6286,13 +6286,13 @@
         <v>5</v>
       </c>
       <c r="L66" s="41" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M66" s="41" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N66" s="41" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="O66" s="41"/>
       <c r="P66" s="41"/>
@@ -6300,20 +6300,20 @@
     </row>
     <row r="67" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="38" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B67" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Evergreen</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D67" s="38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E67" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F67" s="38" t="b">
         <v>0</v>
@@ -6329,13 +6329,13 @@
         <v>9</v>
       </c>
       <c r="L67" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M67" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N67" s="38" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="O67" s="38"/>
       <c r="P67" s="38"/>
@@ -6343,20 +6343,20 @@
     </row>
     <row r="68" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="41" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B68" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Unhatch Being</v>
       </c>
       <c r="C68" s="41" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D68" s="41" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E68" s="41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F68" s="41" t="b">
         <v>0</v>
@@ -6372,13 +6372,13 @@
         <v>6</v>
       </c>
       <c r="L68" s="41" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M68" s="41" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N68" s="41" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O68" s="41"/>
       <c r="P68" s="41"/>
@@ -6386,20 +6386,20 @@
     </row>
     <row r="69" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="38" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B69" s="38" t="str">
         <f t="shared" si="2"/>
         <v>White Dove</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D69" s="38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E69" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F69" s="38" t="b">
         <v>0</v>
@@ -6415,13 +6415,13 @@
         <v>7</v>
       </c>
       <c r="L69" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M69" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N69" s="38" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="O69" s="38"/>
       <c r="P69" s="38"/>
@@ -6429,20 +6429,20 @@
     </row>
     <row r="70" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="41" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B70" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Unquenched Flame</v>
       </c>
       <c r="C70" s="41" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D70" s="41" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E70" s="41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F70" s="41" t="b">
         <v>0</v>
@@ -6458,13 +6458,13 @@
         <v>9</v>
       </c>
       <c r="L70" s="41" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M70" s="41" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N70" s="41" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="O70" s="41"/>
       <c r="P70" s="41"/>
@@ -6472,26 +6472,26 @@
     </row>
     <row r="71" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B71" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Phoenix</v>
       </c>
       <c r="C71" s="38" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D71" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E71" s="38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F71" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G71" s="38" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H71" s="38"/>
       <c r="I71" s="38"/>
@@ -6503,13 +6503,13 @@
         <v>13</v>
       </c>
       <c r="L71" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M71" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N71" s="38" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="O71" s="38"/>
       <c r="P71" s="38"/>
@@ -6517,20 +6517,20 @@
     </row>
     <row r="72" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="41" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B72" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Child</v>
       </c>
       <c r="C72" s="41" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D72" s="41" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E72" s="41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F72" s="41" t="b">
         <v>0</v>
@@ -6546,13 +6546,13 @@
         <v>10</v>
       </c>
       <c r="L72" s="41" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M72" s="41" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N72" s="41" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="O72" s="41"/>
       <c r="P72" s="41"/>
@@ -6560,26 +6560,26 @@
     </row>
     <row r="73" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B73" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Dust-Sealed Heart</v>
       </c>
       <c r="C73" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D73" s="38" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E73" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F73" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G73" s="38" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H73" s="38"/>
       <c r="I73" s="38"/>
@@ -6591,13 +6591,13 @@
         <v>7</v>
       </c>
       <c r="L73" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M73" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N73" s="38" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="O73" s="38"/>
       <c r="P73" s="38"/>
@@ -6605,29 +6605,29 @@
     </row>
     <row r="74" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="41" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B74" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Ronin</v>
       </c>
       <c r="C74" s="41" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D74" s="41" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E74" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F74" s="41" t="b">
         <v>0</v>
       </c>
       <c r="G74" s="41" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H74" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I74" s="41"/>
       <c r="J74" s="41">
@@ -6638,13 +6638,13 @@
         <v>4</v>
       </c>
       <c r="L74" s="41" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M74" s="41" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N74" s="41" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O74" s="41"/>
       <c r="P74" s="41"/>
@@ -6652,29 +6652,29 @@
     </row>
     <row r="75" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B75" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Mortis</v>
       </c>
       <c r="C75" s="38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D75" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E75" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F75" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G75" s="38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H75" s="38" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I75" s="38"/>
       <c r="J75" s="38">
@@ -6685,13 +6685,13 @@
         <v>2</v>
       </c>
       <c r="L75" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M75" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N75" s="38" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="O75" s="38"/>
       <c r="P75" s="38"/>
@@ -6699,26 +6699,26 @@
     </row>
     <row r="76" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="41" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B76" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Slasher</v>
       </c>
       <c r="C76" s="41" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D76" s="41" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E76" s="41" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F76" s="41" t="b">
         <v>0</v>
       </c>
       <c r="G76" s="41" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H76" s="41"/>
       <c r="I76" s="41"/>
@@ -6730,13 +6730,13 @@
         <v>13</v>
       </c>
       <c r="L76" s="41" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="M76" s="41" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N76" s="41" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="O76" s="41"/>
       <c r="P76" s="41"/>
@@ -6744,20 +6744,20 @@
     </row>
     <row r="77" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B77" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Tainted Gipsy</v>
       </c>
       <c r="C77" s="38" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D77" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E77" s="38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F77" s="38" t="b">
         <v>0</v>
@@ -6773,13 +6773,13 @@
         <v>20</v>
       </c>
       <c r="L77" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M77" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N77" s="38" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="O77" s="38"/>
       <c r="P77" s="38"/>
@@ -6787,26 +6787,26 @@
     </row>
     <row r="78" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="41" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B78" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Hall-warden</v>
       </c>
       <c r="C78" s="41" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D78" s="41" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E78" s="41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F78" s="41" t="b">
         <v>0</v>
       </c>
       <c r="G78" s="41" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H78" s="41"/>
       <c r="I78" s="41"/>
@@ -6818,13 +6818,13 @@
         <v>10</v>
       </c>
       <c r="L78" s="41" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M78" s="41" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N78" s="41" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="O78" s="41"/>
       <c r="P78" s="41"/>
@@ -6832,20 +6832,20 @@
     </row>
     <row r="79" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B79" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Athena</v>
       </c>
       <c r="C79" s="38" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D79" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E79" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F79" s="38" t="b">
         <v>0</v>
@@ -6861,13 +6861,13 @@
         <v>12</v>
       </c>
       <c r="L79" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M79" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N79" s="38" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="O79" s="38"/>
       <c r="P79" s="38"/>
@@ -6875,20 +6875,20 @@
     </row>
     <row r="80" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="41" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B80" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Skyburner</v>
       </c>
       <c r="C80" s="41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D80" s="41" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E80" s="41" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F80" s="41" t="b">
         <v>0</v>
@@ -6904,13 +6904,13 @@
         <v>15</v>
       </c>
       <c r="L80" s="41" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M80" s="41" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N80" s="41" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="O80" s="41"/>
       <c r="P80" s="41"/>
@@ -6918,20 +6918,20 @@
     </row>
     <row r="81" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="38" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B81" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Hand of Corruption</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D81" s="38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E81" s="38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F81" s="38" t="b">
         <v>0</v>
@@ -6947,13 +6947,13 @@
         <v>28</v>
       </c>
       <c r="L81" s="38" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="M81" s="38" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N81" s="38" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O81" s="38"/>
       <c r="P81" s="38"/>
@@ -6961,20 +6961,20 @@
     </row>
     <row r="82" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="41" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B82" s="41" t="str">
         <f>A82</f>
         <v>Counter-Blade</v>
       </c>
       <c r="C82" s="41" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="D82" s="41" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E82" s="41" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F82" s="55" t="b">
         <v>1</v>
@@ -6992,13 +6992,13 @@
         <v>12</v>
       </c>
       <c r="L82" s="41" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M82" s="41" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="N82" s="41" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="O82" s="41"/>
       <c r="P82" s="41"/>
@@ -7208,9 +7208,9 @@
     <col min="3" max="3" width="9.33203125" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.25" style="16" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="174.08203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="156.6640625" style="16" customWidth="1"/>
     <col min="7" max="7" width="23.6640625" style="16" customWidth="1"/>
-    <col min="8" max="8" width="12.58203125" style="16" customWidth="1"/>
+    <col min="8" max="8" width="52.25" style="16" customWidth="1"/>
     <col min="9" max="9" width="34.75" style="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="50.08203125" style="16" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.25" style="16" bestFit="1" customWidth="1"/>
@@ -7229,75 +7229,75 @@
         <v>1</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="56" t="s">
+        <v>460</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="56" t="s">
-        <v>464</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="M1" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="22" t="s">
-        <v>33</v>
-      </c>
       <c r="N1" s="22" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="O1" s="22" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" s="26">
         <v>1</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="J2" s="26" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="K2" s="6">
         <v>0</v>
@@ -7316,34 +7316,34 @@
     </row>
     <row r="3" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" s="27">
         <v>1</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F3" s="51" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I3" s="27" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="J3" s="27" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K3" s="16">
         <v>0</v>
@@ -7365,34 +7365,34 @@
     </row>
     <row r="4" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C4" s="26">
         <v>1</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="K4" s="6">
         <v>1</v>
@@ -7414,34 +7414,34 @@
     </row>
     <row r="5" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="27">
         <v>1</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="51" t="s">
-        <v>308</v>
+        <v>39</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>487</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="K5" s="16">
         <v>1</v>
@@ -7463,34 +7463,34 @@
     </row>
     <row r="6" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C6" s="26">
         <v>1</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="26" t="s">
-        <v>443</v>
+      <c r="J6" s="6" t="s">
+        <v>439</v>
       </c>
       <c r="K6" s="6">
         <v>1</v>
@@ -7499,7 +7499,7 @@
         <v>4</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="N6" s="6" t="str">
         <f t="shared" si="1"/>
@@ -7512,34 +7512,34 @@
     </row>
     <row r="7" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7" s="27">
         <v>2</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>317</v>
-      </c>
-      <c r="H7" s="27" t="s">
-        <v>441</v>
+        <v>314</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>314</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="K7" s="16">
         <v>1</v>
@@ -7561,34 +7561,34 @@
     </row>
     <row r="8" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="52">
         <v>2</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E8" s="52" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F8" s="52" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G8" s="52" t="s">
-        <v>317</v>
-      </c>
-      <c r="H8" s="52" t="s">
-        <v>441</v>
+        <v>314</v>
+      </c>
+      <c r="H8" s="66" t="s">
+        <v>314</v>
       </c>
       <c r="I8" s="52" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J8" s="52" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K8" s="61">
         <v>1</v>
@@ -7597,7 +7597,7 @@
         <v>5</v>
       </c>
       <c r="M8" s="52" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N8" s="52" t="str">
         <f t="shared" si="1"/>
@@ -7610,34 +7610,34 @@
     </row>
     <row r="9" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" s="15">
         <v>2</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>312</v>
+        <v>489</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I9" s="57" t="s">
-        <v>421</v>
-      </c>
-      <c r="J9" s="57" t="s">
-        <v>445</v>
+        <v>418</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>441</v>
       </c>
       <c r="K9" s="27">
         <v>2</v>
@@ -7659,34 +7659,34 @@
     </row>
     <row r="10" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="52" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" s="52">
         <v>2</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E10" s="52" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F10" s="52" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G10" s="66" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I10" s="52" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="J10" s="52" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="K10" s="61">
         <v>2</v>
@@ -7708,34 +7708,34 @@
     </row>
     <row r="11" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="15">
         <v>2</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F11" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="G11" s="57" t="s">
         <v>314</v>
       </c>
-      <c r="G11" s="57" t="s">
-        <v>317</v>
-      </c>
       <c r="H11" s="15" t="s">
-        <v>317</v>
-      </c>
-      <c r="I11" s="57" t="s">
-        <v>423</v>
+        <v>314</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>420</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="K11" s="27">
         <v>3</v>
@@ -7744,7 +7744,7 @@
         <v>7</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N11" s="15" t="str">
         <f t="shared" si="1"/>
@@ -7757,34 +7757,34 @@
     </row>
     <row r="12" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" s="52">
         <v>2</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E12" s="52" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G12" s="52" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H12" s="52" t="s">
-        <v>317</v>
-      </c>
-      <c r="I12" s="52" t="s">
-        <v>424</v>
+        <v>314</v>
+      </c>
+      <c r="I12" s="66" t="s">
+        <v>421</v>
       </c>
       <c r="J12" s="52" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="K12" s="61">
         <v>3</v>
@@ -7806,34 +7806,34 @@
     </row>
     <row r="13" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="27">
         <v>3</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="K13" s="16">
         <v>3</v>
@@ -7855,34 +7855,34 @@
     </row>
     <row r="14" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="33" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C14" s="33">
         <v>3</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="K14" s="33">
         <v>4</v>
@@ -7904,34 +7904,34 @@
     </row>
     <row r="15" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C15" s="27">
         <v>3</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I15" s="27" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="K15" s="16">
         <v>4</v>
@@ -7953,34 +7953,34 @@
     </row>
     <row r="16" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="33" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C16" s="33">
         <v>3</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H16" s="33" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I16" s="33" t="s">
         <v>11</v>
       </c>
       <c r="J16" s="33" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="K16" s="33">
         <v>5</v>
@@ -8002,34 +8002,34 @@
     </row>
     <row r="17" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17" s="27">
         <v>3</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I17" s="27" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="J17" s="27" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="K17" s="16">
         <v>5</v>
@@ -8051,34 +8051,34 @@
     </row>
     <row r="18" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="33" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C18" s="33">
         <v>3</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H18" s="33" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I18" s="33" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="J18" s="33" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="K18" s="33">
         <v>5</v>
@@ -8100,34 +8100,34 @@
     </row>
     <row r="19" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C19" s="27">
         <v>3</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I19" s="27" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J19" s="27" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="K19" s="16">
         <v>6</v>
@@ -8149,34 +8149,34 @@
     </row>
     <row r="20" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20" s="39">
         <v>4</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H20" s="39" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="J20" s="39" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="K20" s="39">
         <v>6</v>
@@ -8198,34 +8198,34 @@
     </row>
     <row r="21" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C21" s="27">
         <v>4</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I21" s="27" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="K21" s="16">
         <v>6</v>
@@ -8247,34 +8247,34 @@
     </row>
     <row r="22" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="39" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C22" s="39">
         <v>4</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="J22" s="39" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="K22" s="39">
         <v>6</v>
@@ -8296,34 +8296,34 @@
     </row>
     <row r="23" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C23" s="27">
         <v>4</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I23" s="27" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J23" s="27" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="K23" s="16">
         <v>7</v>
@@ -8345,34 +8345,34 @@
     </row>
     <row r="24" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="39" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C24" s="39">
         <v>4</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E24" s="39" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G24" s="39" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H24" s="39" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I24" s="39" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J24" s="39" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="K24" s="39">
         <v>8</v>
@@ -8394,34 +8394,34 @@
     </row>
     <row r="25" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C25" s="27">
         <v>4</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J25" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="K25" s="16">
         <v>8</v>
@@ -8443,34 +8443,34 @@
     </row>
     <row r="26" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B26" s="41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C26" s="41">
         <v>5</v>
       </c>
       <c r="D26" s="41" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F26" s="41" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G26" s="41" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H26" s="41" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I26" s="41" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J26" s="41" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K26" s="41">
         <v>9</v>
@@ -8492,34 +8492,34 @@
     </row>
     <row r="27" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C27" s="27">
         <v>5</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G27" s="27" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I27" s="27" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="J27" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="K27" s="16">
         <v>9</v>
@@ -8541,34 +8541,34 @@
     </row>
     <row r="28" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="41" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B28" s="41" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C28" s="41">
         <v>5</v>
       </c>
       <c r="D28" s="41" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F28" s="41" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G28" s="67" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="H28" s="41" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I28" s="41" t="s">
         <v>11</v>
       </c>
       <c r="J28" s="41" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K28" s="41">
         <v>10</v>
@@ -8590,34 +8590,34 @@
     </row>
     <row r="29" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C29" s="27">
         <v>5</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I29" s="16" t="s">
         <v>11</v>
       </c>
       <c r="J29" s="27" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="K29" s="16">
         <v>11</v>
@@ -8639,34 +8639,34 @@
     </row>
     <row r="30" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="41" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B30" s="41" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C30" s="41">
         <v>5</v>
       </c>
       <c r="D30" s="41" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E30" s="41" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F30" s="41" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G30" s="67" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="H30" s="41" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I30" s="41" t="s">
         <v>11</v>
       </c>
       <c r="J30" s="41" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="K30" s="41">
         <v>12</v>
@@ -8688,34 +8688,34 @@
     </row>
     <row r="31" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C31" s="27">
         <v>5</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="I31" s="16" t="s">
         <v>11</v>
       </c>
       <c r="J31" s="27" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="K31" s="16">
         <v>12</v>
@@ -8860,6 +8860,6 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Levels.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Levels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CCA\Src\Assets\StreamingAssets\Common\Tables\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6247C4EC-EC8E-4121-BA6E-53C15E5AA14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC35383-6887-4925-B254-DEB5AF804F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="2" r:id="rId1"/>
@@ -1366,19 +1366,11 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>["Intimidation","Void Servant","Devour the Stars","Morphing Remains"]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>["Charge"]</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>["Time Reversal"]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>["Cocooning"]</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -2002,6 +1994,48 @@
       <t>]</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>["</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Time Fasting</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"]</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>["Time Distortion","Void Servant","Devouring Stars","Morphing Remain"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3226,13 +3260,13 @@
         <v>2</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F1" s="22" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="H1" s="22" t="s">
         <v>8</v>
@@ -3297,7 +3331,7 @@
         <v>249</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N2" s="26" t="s">
         <v>356</v>
@@ -3343,7 +3377,7 @@
         <v>12</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N3" s="11" t="s">
         <v>356</v>
@@ -3387,7 +3421,7 @@
         <v>12</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N4" s="7" t="s">
         <v>356</v>
@@ -3433,7 +3467,7 @@
         <v>12</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N5" s="11" t="s">
         <v>356</v>
@@ -3477,10 +3511,10 @@
         <v>249</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
@@ -3507,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>11</v>
@@ -3520,10 +3554,10 @@
         <v>7</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N7" s="29" t="s">
         <v>357</v>
@@ -3567,7 +3601,7 @@
         <v>249</v>
       </c>
       <c r="M8" s="33" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N8" s="33" t="s">
         <v>358</v>
@@ -3597,7 +3631,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>16</v>
@@ -3616,7 +3650,7 @@
         <v>12</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N9" s="11" t="s">
         <v>356</v>
@@ -3643,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="32" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="H10" s="32" t="s">
         <v>16</v>
@@ -3662,7 +3696,7 @@
         <v>12</v>
       </c>
       <c r="M10" s="32" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N10" s="32" t="s">
         <v>356</v>
@@ -3709,7 +3743,7 @@
         <v>12</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N11" s="11" t="s">
         <v>356</v>
@@ -3753,7 +3787,7 @@
         <v>12</v>
       </c>
       <c r="M12" s="32" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N12" s="32" t="s">
         <v>356</v>
@@ -3771,7 +3805,7 @@
         <v>Skunk Chieftain</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>224</v>
@@ -3802,7 +3836,7 @@
         <v>354</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N13" s="11" t="s">
         <v>359</v>
@@ -3846,10 +3880,10 @@
         <v>249</v>
       </c>
       <c r="M14" s="33" t="s">
-        <v>417</v>
-      </c>
-      <c r="N14" s="33" t="s">
-        <v>360</v>
+        <v>415</v>
+      </c>
+      <c r="N14" s="32" t="s">
+        <v>490</v>
       </c>
       <c r="O14" s="33"/>
       <c r="P14" s="33"/>
@@ -3895,10 +3929,10 @@
         <v>245</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N15" s="29" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3941,10 +3975,10 @@
         <v>12</v>
       </c>
       <c r="M16" s="32" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N16" s="33" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="O16" s="32"/>
       <c r="P16" s="32"/>
@@ -3962,7 +3996,7 @@
         <v>101</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>232</v>
@@ -3990,10 +4024,10 @@
         <v>12</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>417</v>
-      </c>
-      <c r="N17" s="29" t="s">
-        <v>363</v>
+        <v>415</v>
+      </c>
+      <c r="N17" s="11" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4029,10 +4063,10 @@
         <v>12</v>
       </c>
       <c r="M18" s="32" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N18" s="33" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="O18" s="32"/>
       <c r="P18" s="32"/>
@@ -4076,7 +4110,7 @@
         <v>12</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N19" s="11" t="s">
         <v>356</v>
@@ -4117,13 +4151,13 @@
         <v>2</v>
       </c>
       <c r="L20" s="33" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="M20" s="32" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N20" s="33" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="O20" s="32"/>
       <c r="P20" s="32"/>
@@ -4150,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H21" s="11" t="s">
         <v>11</v>
@@ -4169,10 +4203,10 @@
         <v>354</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N21" s="29" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4215,10 +4249,10 @@
         <v>12</v>
       </c>
       <c r="M22" s="34" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N22" s="53" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="O22" s="34"/>
       <c r="P22" s="34"/>
@@ -4264,10 +4298,10 @@
         <v>249</v>
       </c>
       <c r="M23" s="29" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N23" s="29" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="O23" s="29"/>
       <c r="P23" s="29"/>
@@ -4313,7 +4347,7 @@
         <v>249</v>
       </c>
       <c r="M24" s="34" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N24" s="34" t="s">
         <v>356</v>
@@ -4360,10 +4394,10 @@
         <v>249</v>
       </c>
       <c r="M25" s="29" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N25" s="29" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="O25" s="29"/>
       <c r="P25" s="29"/>
@@ -4407,7 +4441,7 @@
         <v>12</v>
       </c>
       <c r="M26" s="34" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N26" s="34" t="s">
         <v>356</v>
@@ -4454,10 +4488,10 @@
         <v>249</v>
       </c>
       <c r="M27" s="29" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N27" s="29" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="O27" s="29"/>
       <c r="P27" s="29"/>
@@ -4503,7 +4537,7 @@
         <v>12</v>
       </c>
       <c r="M28" s="34" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N28" s="34" t="s">
         <v>356</v>
@@ -4552,7 +4586,7 @@
         <v>249</v>
       </c>
       <c r="M29" s="29" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N29" s="29" t="s">
         <v>356</v>
@@ -4601,7 +4635,7 @@
         <v>249</v>
       </c>
       <c r="M30" s="34" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N30" s="34" t="s">
         <v>356</v>
@@ -4648,10 +4682,10 @@
         <v>249</v>
       </c>
       <c r="M31" s="29" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N31" s="29" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="O31" s="29"/>
       <c r="P31" s="29"/>
@@ -4678,7 +4712,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="53" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>11</v>
@@ -4697,10 +4731,10 @@
         <v>249</v>
       </c>
       <c r="M32" s="34" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N32" s="53" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="O32" s="34"/>
       <c r="P32" s="34"/>
@@ -4727,7 +4761,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="29" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H33" s="29" t="s">
         <v>11</v>
@@ -4746,10 +4780,10 @@
         <v>249</v>
       </c>
       <c r="M33" s="29" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N33" s="29" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="O33" s="29"/>
       <c r="P33" s="29"/>
@@ -4776,7 +4810,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H34" s="34" t="s">
         <v>11</v>
@@ -4795,10 +4829,10 @@
         <v>12</v>
       </c>
       <c r="M34" s="34" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N34" s="53" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="O34" s="34"/>
       <c r="P34" s="34"/>
@@ -4844,10 +4878,10 @@
         <v>249</v>
       </c>
       <c r="M35" s="29" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N35" s="29" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="O35" s="29"/>
       <c r="P35" s="29"/>
@@ -4891,10 +4925,10 @@
         <v>249</v>
       </c>
       <c r="M36" s="34" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N36" s="53" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="O36" s="34"/>
       <c r="P36" s="34"/>
@@ -4938,10 +4972,10 @@
         <v>249</v>
       </c>
       <c r="M37" s="29" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N37" s="29" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="O37" s="29"/>
       <c r="P37" s="29"/>
@@ -4985,10 +5019,10 @@
         <v>249</v>
       </c>
       <c r="M38" s="37" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N38" s="37" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="O38" s="37"/>
       <c r="P38" s="37"/>
@@ -5034,7 +5068,7 @@
         <v>12</v>
       </c>
       <c r="M39" s="11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N39" s="29" t="s">
         <v>356</v>
@@ -5078,10 +5112,10 @@
         <v>249</v>
       </c>
       <c r="M40" s="39" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N40" s="39" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="O40" s="39"/>
       <c r="P40" s="39"/>
@@ -5127,10 +5161,10 @@
         <v>249</v>
       </c>
       <c r="M41" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N41" s="38" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="O41" s="38"/>
       <c r="P41" s="38"/>
@@ -5176,10 +5210,10 @@
         <v>249</v>
       </c>
       <c r="M42" s="39" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N42" s="39" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="O42" s="39"/>
       <c r="P42" s="39"/>
@@ -5222,13 +5256,13 @@
         <v>2</v>
       </c>
       <c r="L43" s="38" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="M43" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N43" s="38" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="O43" s="38"/>
       <c r="P43" s="38"/>
@@ -5258,7 +5292,7 @@
         <v>241</v>
       </c>
       <c r="H44" s="39" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="I44" s="39" t="s">
         <v>11</v>
@@ -5274,10 +5308,10 @@
         <v>249</v>
       </c>
       <c r="M44" s="39" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N44" s="39" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="O44" s="39"/>
       <c r="P44" s="39"/>
@@ -5320,13 +5354,13 @@
         <v>3</v>
       </c>
       <c r="L45" s="38" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="M45" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N45" s="38" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="O45" s="38"/>
       <c r="P45" s="38"/>
@@ -5372,10 +5406,10 @@
         <v>249</v>
       </c>
       <c r="M46" s="39" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N46" s="39" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="O46" s="39"/>
       <c r="P46" s="39"/>
@@ -5421,10 +5455,10 @@
         <v>249</v>
       </c>
       <c r="M47" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N47" s="38" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="O47" s="38"/>
       <c r="P47" s="38"/>
@@ -5470,10 +5504,10 @@
         <v>249</v>
       </c>
       <c r="M48" s="39" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N48" s="39" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="O48" s="39"/>
       <c r="P48" s="39"/>
@@ -5519,10 +5553,10 @@
         <v>249</v>
       </c>
       <c r="M49" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N49" s="38" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="O49" s="38"/>
       <c r="P49" s="38"/>
@@ -5568,10 +5602,10 @@
         <v>249</v>
       </c>
       <c r="M50" s="39" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N50" s="39" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="O50" s="39"/>
       <c r="P50" s="39"/>
@@ -5615,10 +5649,10 @@
         <v>249</v>
       </c>
       <c r="M51" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N51" s="38" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="O51" s="38"/>
       <c r="P51" s="38"/>
@@ -5660,10 +5694,10 @@
         <v>249</v>
       </c>
       <c r="M52" s="39" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N52" s="39" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="O52" s="39"/>
       <c r="P52" s="39"/>
@@ -5705,10 +5739,10 @@
         <v>249</v>
       </c>
       <c r="M53" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N53" s="38" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="O53" s="38"/>
       <c r="P53" s="38"/>
@@ -5752,10 +5786,10 @@
         <v>249</v>
       </c>
       <c r="M54" s="39" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N54" s="39" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="O54" s="39"/>
       <c r="P54" s="39"/>
@@ -5799,10 +5833,10 @@
         <v>249</v>
       </c>
       <c r="M55" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N55" s="38" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="O55" s="38"/>
       <c r="P55" s="38"/>
@@ -5845,13 +5879,13 @@
         <v>8</v>
       </c>
       <c r="L56" s="39" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="M56" s="39" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N56" s="39" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="O56" s="39"/>
       <c r="P56" s="39"/>
@@ -5897,10 +5931,10 @@
         <v>249</v>
       </c>
       <c r="M57" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N57" s="38" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="O57" s="38"/>
       <c r="P57" s="38"/>
@@ -5946,10 +5980,10 @@
         <v>249</v>
       </c>
       <c r="M58" s="39" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N58" s="39" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="O58" s="39"/>
       <c r="P58" s="39"/>
@@ -5987,10 +6021,10 @@
         <v>12</v>
       </c>
       <c r="M59" s="11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N59" s="29" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6027,10 +6061,10 @@
         <v>249</v>
       </c>
       <c r="M60" s="41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N60" s="41" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="O60" s="41"/>
       <c r="P60" s="41"/>
@@ -6072,10 +6106,10 @@
         <v>249</v>
       </c>
       <c r="M61" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N61" s="38" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="O61" s="38"/>
       <c r="P61" s="38"/>
@@ -6117,10 +6151,10 @@
         <v>249</v>
       </c>
       <c r="M62" s="41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N62" s="41" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="O62" s="41"/>
       <c r="P62" s="41"/>
@@ -6160,10 +6194,10 @@
         <v>249</v>
       </c>
       <c r="M63" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N63" s="38" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O63" s="38"/>
       <c r="P63" s="38"/>
@@ -6203,10 +6237,10 @@
         <v>249</v>
       </c>
       <c r="M64" s="41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N64" s="41" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="O64" s="41"/>
       <c r="P64" s="41"/>
@@ -6246,10 +6280,10 @@
         <v>249</v>
       </c>
       <c r="M65" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N65" s="38" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="O65" s="38"/>
       <c r="P65" s="38"/>
@@ -6289,10 +6323,10 @@
         <v>249</v>
       </c>
       <c r="M66" s="41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N66" s="41" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="O66" s="41"/>
       <c r="P66" s="41"/>
@@ -6332,10 +6366,10 @@
         <v>249</v>
       </c>
       <c r="M67" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N67" s="38" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="O67" s="38"/>
       <c r="P67" s="38"/>
@@ -6375,10 +6409,10 @@
         <v>249</v>
       </c>
       <c r="M68" s="41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N68" s="41" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="O68" s="41"/>
       <c r="P68" s="41"/>
@@ -6418,10 +6452,10 @@
         <v>249</v>
       </c>
       <c r="M69" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N69" s="38" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="O69" s="38"/>
       <c r="P69" s="38"/>
@@ -6461,10 +6495,10 @@
         <v>249</v>
       </c>
       <c r="M70" s="41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N70" s="41" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="O70" s="41"/>
       <c r="P70" s="41"/>
@@ -6506,10 +6540,10 @@
         <v>249</v>
       </c>
       <c r="M71" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N71" s="38" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="O71" s="38"/>
       <c r="P71" s="38"/>
@@ -6549,10 +6583,10 @@
         <v>249</v>
       </c>
       <c r="M72" s="41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N72" s="41" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="O72" s="41"/>
       <c r="P72" s="41"/>
@@ -6594,10 +6628,10 @@
         <v>249</v>
       </c>
       <c r="M73" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N73" s="38" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="O73" s="38"/>
       <c r="P73" s="38"/>
@@ -6641,10 +6675,10 @@
         <v>249</v>
       </c>
       <c r="M74" s="41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N74" s="41" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="O74" s="41"/>
       <c r="P74" s="41"/>
@@ -6688,10 +6722,10 @@
         <v>249</v>
       </c>
       <c r="M75" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N75" s="38" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="O75" s="38"/>
       <c r="P75" s="38"/>
@@ -6730,13 +6764,13 @@
         <v>13</v>
       </c>
       <c r="L76" s="41" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="M76" s="41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N76" s="41" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="O76" s="41"/>
       <c r="P76" s="41"/>
@@ -6776,10 +6810,10 @@
         <v>249</v>
       </c>
       <c r="M77" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N77" s="38" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="O77" s="38"/>
       <c r="P77" s="38"/>
@@ -6821,10 +6855,10 @@
         <v>249</v>
       </c>
       <c r="M78" s="41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N78" s="41" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="O78" s="41"/>
       <c r="P78" s="41"/>
@@ -6864,10 +6898,10 @@
         <v>249</v>
       </c>
       <c r="M79" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N79" s="38" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="O79" s="38"/>
       <c r="P79" s="38"/>
@@ -6907,10 +6941,10 @@
         <v>249</v>
       </c>
       <c r="M80" s="41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N80" s="41" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="O80" s="41"/>
       <c r="P80" s="41"/>
@@ -6947,13 +6981,13 @@
         <v>28</v>
       </c>
       <c r="L81" s="38" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="M81" s="38" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N81" s="38" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="O81" s="38"/>
       <c r="P81" s="38"/>
@@ -6961,14 +6995,14 @@
     </row>
     <row r="82" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="41" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B82" s="41" t="str">
         <f>A82</f>
         <v>Counter-Blade</v>
       </c>
       <c r="C82" s="41" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D82" s="41" t="s">
         <v>227</v>
@@ -6995,10 +7029,10 @@
         <v>249</v>
       </c>
       <c r="M82" s="41" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N82" s="41" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="O82" s="41"/>
       <c r="P82" s="41"/>
@@ -7250,7 +7284,7 @@
         <v>29</v>
       </c>
       <c r="J1" s="56" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>30</v>
@@ -7262,10 +7296,10 @@
         <v>32</v>
       </c>
       <c r="N1" s="22" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="O1" s="22" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7294,7 +7328,7 @@
         <v>314</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="J2" s="26" t="s">
         <v>314</v>
@@ -7340,10 +7374,10 @@
         <v>314</v>
       </c>
       <c r="I3" s="27" t="s">
+        <v>434</v>
+      </c>
+      <c r="J3" s="27" t="s">
         <v>436</v>
-      </c>
-      <c r="J3" s="27" t="s">
-        <v>438</v>
       </c>
       <c r="K3" s="16">
         <v>0</v>
@@ -7389,7 +7423,7 @@
         <v>314</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="J4" s="6" t="s">
         <v>314</v>
@@ -7429,16 +7463,16 @@
         <v>39</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H5" s="16" t="s">
         <v>314</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J5" s="16" t="s">
         <v>314</v>
@@ -7490,7 +7524,7 @@
         <v>11</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K6" s="6">
         <v>1</v>
@@ -7499,7 +7533,7 @@
         <v>4</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="N6" s="6" t="str">
         <f t="shared" si="1"/>
@@ -7536,10 +7570,10 @@
         <v>314</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K7" s="16">
         <v>1</v>
@@ -7588,7 +7622,7 @@
         <v>42</v>
       </c>
       <c r="J8" s="52" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K8" s="61">
         <v>1</v>
@@ -7597,7 +7631,7 @@
         <v>5</v>
       </c>
       <c r="M8" s="52" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="N8" s="52" t="str">
         <f t="shared" si="1"/>
@@ -7625,7 +7659,7 @@
         <v>281</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G9" s="15" t="s">
         <v>314</v>
@@ -7634,10 +7668,10 @@
         <v>314</v>
       </c>
       <c r="I9" s="57" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="K9" s="27">
         <v>2</v>
@@ -7677,13 +7711,13 @@
         <v>310</v>
       </c>
       <c r="G10" s="66" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="H10" s="52" t="s">
         <v>314</v>
       </c>
       <c r="I10" s="52" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="J10" s="52" t="s">
         <v>314</v>
@@ -7732,10 +7766,10 @@
         <v>314</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K11" s="27">
         <v>3</v>
@@ -7781,10 +7815,10 @@
         <v>314</v>
       </c>
       <c r="I12" s="66" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J12" s="52" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="K12" s="61">
         <v>3</v>
@@ -7830,10 +7864,10 @@
         <v>314</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="K13" s="16">
         <v>3</v>
@@ -7879,10 +7913,10 @@
         <v>314</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="K14" s="33">
         <v>4</v>
@@ -7928,10 +7962,10 @@
         <v>314</v>
       </c>
       <c r="I15" s="27" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="K15" s="16">
         <v>4</v>
@@ -7980,7 +8014,7 @@
         <v>11</v>
       </c>
       <c r="J16" s="33" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="K16" s="33">
         <v>5</v>
@@ -8026,10 +8060,10 @@
         <v>314</v>
       </c>
       <c r="I17" s="27" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J17" s="27" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="K17" s="16">
         <v>5</v>
@@ -8075,10 +8109,10 @@
         <v>314</v>
       </c>
       <c r="I18" s="33" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J18" s="33" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="K18" s="33">
         <v>5</v>
@@ -8127,7 +8161,7 @@
         <v>314</v>
       </c>
       <c r="J19" s="27" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K19" s="16">
         <v>6</v>
@@ -8173,10 +8207,10 @@
         <v>314</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="J20" s="39" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="K20" s="39">
         <v>6</v>
@@ -8222,7 +8256,7 @@
         <v>314</v>
       </c>
       <c r="I21" s="27" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="J21" s="16" t="s">
         <v>314</v>
@@ -8271,10 +8305,10 @@
         <v>314</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="J22" s="39" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K22" s="39">
         <v>6</v>
@@ -8323,7 +8357,7 @@
         <v>314</v>
       </c>
       <c r="J23" s="27" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K23" s="16">
         <v>7</v>
@@ -8372,7 +8406,7 @@
         <v>314</v>
       </c>
       <c r="J24" s="39" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K24" s="39">
         <v>8</v>
@@ -8470,7 +8504,7 @@
         <v>314</v>
       </c>
       <c r="J26" s="41" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K26" s="41">
         <v>9</v>
@@ -8516,7 +8550,7 @@
         <v>314</v>
       </c>
       <c r="I27" s="27" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="J27" s="16" t="s">
         <v>314</v>
@@ -8559,7 +8593,7 @@
         <v>345</v>
       </c>
       <c r="G28" s="67" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H28" s="41" t="s">
         <v>314</v>
@@ -8568,7 +8602,7 @@
         <v>11</v>
       </c>
       <c r="J28" s="41" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K28" s="41">
         <v>10</v>
@@ -8608,7 +8642,7 @@
         <v>346</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H29" s="16" t="s">
         <v>314</v>
@@ -8617,7 +8651,7 @@
         <v>11</v>
       </c>
       <c r="J29" s="27" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K29" s="16">
         <v>11</v>
@@ -8657,7 +8691,7 @@
         <v>347</v>
       </c>
       <c r="G30" s="67" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H30" s="41" t="s">
         <v>314</v>
@@ -8666,7 +8700,7 @@
         <v>11</v>
       </c>
       <c r="J30" s="41" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K30" s="41">
         <v>12</v>
@@ -8706,7 +8740,7 @@
         <v>348</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H31" s="16" t="s">
         <v>314</v>
@@ -8715,7 +8749,7 @@
         <v>11</v>
       </c>
       <c r="J31" s="27" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K31" s="16">
         <v>12</v>
